--- a/public/downloads/beschlagsliste.xlsx
+++ b/public/downloads/beschlagsliste.xlsx
@@ -18,6 +18,7 @@
         <b/>
         <color rgb="FF1B1712"/>
         <sz val="14"/>
+        <rFont val="Space Grotesk"/>
       </rPr>
       <t>schreiner</t>
     </r>
@@ -26,6 +27,7 @@
         <b/>
         <color rgb="FFFF7A1A"/>
         <sz val="14"/>
+        <rFont val="Space Grotesk"/>
       </rPr>
       <t>.digital</t>
     </r>
